--- a/Rekap.xlsx
+++ b/Rekap.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\wahid idea\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A350631-6BF3-4F58-8A52-F118908897FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B459171-68BB-46F7-96D8-5BAEA740C86F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data Pasien" sheetId="1" r:id="rId1"/>
@@ -20,24 +20,49 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Nama Pasien</t>
+  </si>
+  <si>
+    <t>Tanggal Pemeriksaan</t>
+  </si>
+  <si>
+    <t>ID Pasien</t>
+  </si>
+  <si>
+    <t>Umur</t>
+  </si>
+  <si>
+    <t>Jenis Kelamin</t>
+  </si>
+  <si>
+    <t>Jenis Pemeriksaan</t>
+  </si>
+  <si>
+    <t>Tagangan (kV)</t>
+  </si>
+  <si>
+    <t>CTDIvol</t>
+  </si>
+  <si>
+    <t>Total DLP</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -60,12 +85,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -368,7 +389,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -380,25 +401,37 @@
     <col min="7" max="8" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Rekap.xlsx
+++ b/Rekap.xlsx
@@ -1,76 +1,47 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\wahid idea\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B459171-68BB-46F7-96D8-5BAEA740C86F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="10236" yWindow="0" windowWidth="11520" windowHeight="12240" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Data Pasien" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Pasien" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Nama Pasien</t>
-  </si>
-  <si>
-    <t>Tanggal Pemeriksaan</t>
-  </si>
-  <si>
-    <t>ID Pasien</t>
-  </si>
-  <si>
-    <t>Umur</t>
-  </si>
-  <si>
-    <t>Jenis Kelamin</t>
-  </si>
-  <si>
-    <t>Jenis Pemeriksaan</t>
-  </si>
-  <si>
-    <t>Tagangan (kV)</t>
-  </si>
-  <si>
-    <t>CTDIvol</t>
-  </si>
-  <si>
-    <t>Total DLP</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -85,22 +56,84 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -388,49 +421,137 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="25" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="30" customWidth="1"/>
-    <col min="7" max="8" width="15" customWidth="1"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="8"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Tanggal Upload</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Nama Pasien</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Tanggal Pemeriksaan</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>ID Pasien</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Umur Pasien</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Jenis Kelamin</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Jenis Pemeriksaan</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Tegangan (kV)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>CTDIvol (mGy)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Total DLP (mGy·cm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-04-02 21:23:26</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ABDUL RAHMAN. TN</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>02 Feb 2026</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>680322</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>26 Tahun</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Laki-laki</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>CT KEPALA</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>44.38</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>1250.42</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Rekap.xlsx
+++ b/Rekap.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -554,6 +554,61 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-04-02 21:24:43</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>PENI FATMAWATI. NY</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>02 Feb 2026</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>652672</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>26 Tahun</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Perempuan</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>CT KEPALA + KONTRAS</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>44.38</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2586.24</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Rekap.xlsx
+++ b/Rekap.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,17 +25,29 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4472C4"/>
+        <bgColor rgb="FF4472C4"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -56,9 +68,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -434,66 +449,66 @@
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="8"/>
+    <col width="12" customWidth="1" min="6" max="7"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="10" max="11"/>
     <col width="15" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Tanggal Upload</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Nama Pasien</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Tanggal Pemeriksaan</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>ID Pasien</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Umur Pasien</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Jenis Kelamin</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Jenis Pemeriksaan</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Tegangan (kV)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>CTDIvol (mGy)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>Total DLP (mGy·cm)</t>
         </is>
@@ -505,7 +520,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-04-02 21:23:26</t>
+          <t>2026-04-03 09:38:49</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -523,10 +538,8 @@
           <t>680322</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>26 Tahun</t>
-        </is>
+      <c r="F2" t="n">
+        <v>26</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -560,7 +573,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-04-02 21:24:43</t>
+          <t>2026-04-03 09:39:14</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -578,10 +591,8 @@
           <t>652672</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>26 Tahun</t>
-        </is>
+      <c r="F3" t="n">
+        <v>26</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>

--- a/Rekap.xlsx
+++ b/Rekap.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -514,112 +514,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-04-03 09:38:49</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>ABDUL RAHMAN. TN</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>02 Feb 2026</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>680322</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>26</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Laki-laki</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>CT KEPALA</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>44.38</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>1250.42</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-04-03 09:39:14</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>PENI FATMAWATI. NY</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>02 Feb 2026</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>652672</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>26</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Perempuan</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>CT KEPALA + KONTRAS</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>44.38</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2586.24</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
